--- a/pkg/SampleData/framingham_wilson.xlsx
+++ b/pkg/SampleData/framingham_wilson.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="18" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -4309,7 +4309,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -5472,7 +5472,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>
